--- a/Excel/Software.xlsx
+++ b/Excel/Software.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Projects\#PowerShell\Software Installer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\My Projects\PowerShell\SoftwareInstaller\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE425867-09C7-4686-BA79-54E0A3193F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB0F265-DA7A-4F2F-B87D-3C214F4C6AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="3690" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Software" sheetId="7" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Data" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Software!$A$1:$E$405</definedName>
+    <definedName name="ExternalData_1" localSheetId="0" hidden="1">Software!$A$1:$E$407</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3313" uniqueCount="865">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3321" uniqueCount="869">
   <si>
     <t>Name</t>
   </si>
@@ -2661,6 +2661,18 @@
   </si>
   <si>
     <t>WiresharkFoundation.Stratoshark</t>
+  </si>
+  <si>
+    <t>Ookla.Speedtest.CLI</t>
+  </si>
+  <si>
+    <t>Ookla Speedtest CLI</t>
+  </si>
+  <si>
+    <t>Axialis.IconWorkshop</t>
+  </si>
+  <si>
+    <t>Axialis IconWorkshop</t>
   </si>
 </sst>
 </file>
@@ -2771,8 +2783,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D2783BDA-2C42-4587-9D04-23A48F282058}" name="Software" displayName="Software" ref="A1:E405" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:E405" xr:uid="{D2783BDA-2C42-4587-9D04-23A48F282058}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{D2783BDA-2C42-4587-9D04-23A48F282058}" name="Software" displayName="Software" ref="A1:E407" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:E407" xr:uid="{D2783BDA-2C42-4587-9D04-23A48F282058}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E405">
     <sortCondition ref="A1:A405"/>
   </sortState>
@@ -3076,7 +3088,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80367ABE-3C1D-4C7C-8CEA-B7186804BADD}">
-  <dimension ref="A1:E405"/>
+  <dimension ref="A1:E407"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" bestFit="1" customWidth="1"/>
@@ -9488,11 +9500,10 @@
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A389" s="5" t="s">
+      <c r="A389" t="s">
         <v>863</v>
       </c>
-      <c r="B389" s="6"/>
-      <c r="C389" s="5" t="s">
+      <c r="C389" t="s">
         <v>864</v>
       </c>
       <c r="D389" t="s">
@@ -9759,9 +9770,38 @@
         <v>9</v>
       </c>
     </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A406" t="s">
+        <v>866</v>
+      </c>
+      <c r="C406" t="s">
+        <v>865</v>
+      </c>
+      <c r="D406" t="s">
+        <v>21</v>
+      </c>
+      <c r="E406" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A407" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="B407" s="6"/>
+      <c r="C407" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="D407" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="E407" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E405" xr:uid="{1947938B-6FC1-4B02-989F-E6856B64DA37}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E407" xr:uid="{1947938B-6FC1-4B02-989F-E6856B64DA37}">
       <formula1>"winget, scoop, choco"</formula1>
     </dataValidation>
   </dataValidations>
@@ -9776,7 +9816,7 @@
           <x14:formula1>
             <xm:f>Data!$A$2:$A$40</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D405</xm:sqref>
+          <xm:sqref>D2:D407</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
